--- a/artfynd/A 41081-2024 artfynd.xlsx
+++ b/artfynd/A 41081-2024 artfynd.xlsx
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119540506</v>
+        <v>119540503</v>
       </c>
       <c r="B12" t="n">
         <v>90562</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628479</v>
+        <v>628314</v>
       </c>
       <c r="R12" t="n">
-        <v>6955272</v>
+        <v>6955333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
+          <t>drygt 100-årig blåbärsgranskog med vindfällen av gran</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -1855,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119540503</v>
+        <v>119540506</v>
       </c>
       <c r="B13" t="n">
         <v>90562</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628314</v>
+        <v>628479</v>
       </c>
       <c r="R13" t="n">
-        <v>6955333</v>
+        <v>6955272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>drygt 100-årig blåbärsgranskog med vindfällen av gran</t>
+          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119540511</v>
+        <v>119540509</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>90752</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,25 +1987,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628469</v>
+        <v>628516</v>
       </c>
       <c r="R14" t="n">
-        <v>6955210</v>
+        <v>6955194</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
+          <t>drygt 100-årig, tät blåbärsgranskog med gott om död gran och äldre björk</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>förrötad grov granlåga</t>
+          <t>förrötad grov granlåga med mesta barken kvar</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119540509</v>
+        <v>119540511</v>
       </c>
       <c r="B15" t="n">
-        <v>90752</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628516</v>
+        <v>628469</v>
       </c>
       <c r="R15" t="n">
-        <v>6955194</v>
+        <v>6955210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>drygt 100-årig, tät blåbärsgranskog med gott om död gran och äldre björk</t>
+          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>förrötad grov granlåga med mesta barken kvar</t>
+          <t>förrötad grov granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 41081-2024 artfynd.xlsx
+++ b/artfynd/A 41081-2024 artfynd.xlsx
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119540503</v>
+        <v>119540511</v>
       </c>
       <c r="B12" t="n">
         <v>90562</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628314</v>
+        <v>628469</v>
       </c>
       <c r="R12" t="n">
-        <v>6955333</v>
+        <v>6955210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>drygt 100-årig blåbärsgranskog med vindfällen av gran</t>
+          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>förrötad granlåga</t>
+          <t>förrötad grov granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119540506</v>
+        <v>119540503</v>
       </c>
       <c r="B13" t="n">
         <v>90562</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628479</v>
+        <v>628314</v>
       </c>
       <c r="R13" t="n">
-        <v>6955272</v>
+        <v>6955333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
+          <t>drygt 100-årig blåbärsgranskog med vindfällen av gran</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119540509</v>
+        <v>119540506</v>
       </c>
       <c r="B14" t="n">
-        <v>90752</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,25 +1987,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628516</v>
+        <v>628479</v>
       </c>
       <c r="R14" t="n">
-        <v>6955194</v>
+        <v>6955272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>drygt 100-årig, tät blåbärsgranskog med gott om död gran och äldre björk</t>
+          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>förrötad grov granlåga med mesta barken kvar</t>
+          <t>förrötad granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119540511</v>
+        <v>119540510</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628469</v>
+        <v>628475</v>
       </c>
       <c r="R15" t="n">
-        <v>6955210</v>
+        <v>6955207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>förrötad grov granlåga</t>
+          <t>förrötad grov och äldre granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119540510</v>
+        <v>119540509</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>90752</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628475</v>
+        <v>628516</v>
       </c>
       <c r="R16" t="n">
-        <v>6955207</v>
+        <v>6955194</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>drygt 100-årig blåbärsgranskog med barkborreluckor</t>
+          <t>drygt 100-årig, tät blåbärsgranskog med gott om död gran och äldre björk</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>förrötad grov och äldre granlåga</t>
+          <t>förrötad grov granlåga med mesta barken kvar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
